--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F693D6F-C2AE-43D9-94FF-1AA9E9B2410A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A276D1A6-D8DC-4DD4-AF49-8E89AF6D371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6390" uniqueCount="6345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6399" uniqueCount="6354">
   <si>
     <t>Fecha</t>
   </si>
@@ -19023,10 +19023,37 @@
     <t>2026/02/23</t>
   </si>
   <si>
+    <t>2026/02/24</t>
+  </si>
+  <si>
+    <t>2026/02/25</t>
+  </si>
+  <si>
+    <t>2026/02/26</t>
+  </si>
+  <si>
+    <t>2026/02/27</t>
+  </si>
+  <si>
+    <t>2026/02/28</t>
+  </si>
+  <si>
+    <t>2026/03/01</t>
+  </si>
+  <si>
+    <t>2026/03/02</t>
+  </si>
+  <si>
+    <t>2026/03/03</t>
+  </si>
+  <si>
+    <t>2026/03/04</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República martes, 24 de febrero de 2026 8:12:13 a. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 5 de marzo de 2026 8:47:52 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19442,7 +19469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6308"/>
+  <dimension ref="A1:B6317"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -69892,15 +69919,87 @@
       <c r="A6306" t="s">
         <v>6335</v>
       </c>
+      <c r="B6306" s="1">
+        <v>4353.0867900000003</v>
+      </c>
     </row>
     <row r="6307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6307" t="s">
-        <v>6335</v>
+        <v>6336</v>
+      </c>
+      <c r="B6307" s="1">
+        <v>4370.4258900000004</v>
       </c>
     </row>
     <row r="6308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6308" t="s">
-        <v>6336</v>
+        <v>6337</v>
+      </c>
+      <c r="B6308" s="1">
+        <v>4369.79864</v>
+      </c>
+    </row>
+    <row r="6309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6309" t="s">
+        <v>6338</v>
+      </c>
+      <c r="B6309" s="1">
+        <v>4422.6424399999996</v>
+      </c>
+    </row>
+    <row r="6310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6310" t="s">
+        <v>6339</v>
+      </c>
+      <c r="B6310" s="1">
+        <v>4446.8704100000004</v>
+      </c>
+    </row>
+    <row r="6311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6311" t="s">
+        <v>6340</v>
+      </c>
+      <c r="B6311" s="1">
+        <v>4446.8704100000004</v>
+      </c>
+    </row>
+    <row r="6312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6312" t="s">
+        <v>6341</v>
+      </c>
+      <c r="B6312" s="1">
+        <v>4399.0384000000004</v>
+      </c>
+    </row>
+    <row r="6313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6313" t="s">
+        <v>6342</v>
+      </c>
+      <c r="B6313" s="1">
+        <v>4361.7396600000002</v>
+      </c>
+    </row>
+    <row r="6314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6314" t="s">
+        <v>6343</v>
+      </c>
+      <c r="B6314" s="1">
+        <v>4420.26307</v>
+      </c>
+    </row>
+    <row r="6315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6315" t="s">
+        <v>6344</v>
+      </c>
+    </row>
+    <row r="6316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6316" t="s">
+        <v>6344</v>
+      </c>
+    </row>
+    <row r="6317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6317" t="s">
+        <v>6345</v>
       </c>
     </row>
   </sheetData>
@@ -69923,19 +70022,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6337</v>
+        <v>6346</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6338</v>
+        <v>6347</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6339</v>
+        <v>6348</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6340</v>
+        <v>6349</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6341</v>
+        <v>6350</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -69946,13 +70045,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -69963,13 +70062,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -69980,13 +70079,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -69997,13 +70096,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70014,13 +70113,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70031,13 +70130,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70048,13 +70147,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70065,13 +70164,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70082,13 +70181,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70099,13 +70198,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70116,13 +70215,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70133,13 +70232,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70150,13 +70249,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70167,13 +70266,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70184,13 +70283,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6342</v>
+        <v>6351</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6343</v>
+        <v>6352</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6344</v>
+        <v>6353</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A276D1A6-D8DC-4DD4-AF49-8E89AF6D371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B47B45-0502-4118-B239-311A04C3517F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,12 +11,25 @@
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
     <sheet name="Información" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6399" uniqueCount="6354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6404" uniqueCount="6359">
   <si>
     <t>Fecha</t>
   </si>
@@ -19050,10 +19063,25 @@
     <t>2026/03/04</t>
   </si>
   <si>
+    <t>2026/03/05</t>
+  </si>
+  <si>
+    <t>2026/03/06</t>
+  </si>
+  <si>
+    <t>2026/03/07</t>
+  </si>
+  <si>
+    <t>2026/03/08</t>
+  </si>
+  <si>
+    <t>2026/03/09</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 5 de marzo de 2026 8:47:52 a. m.</t>
+    <t>Descargado de sistema del Banco de la República martes, 10 de marzo de 2026 10:26:32 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19099,6 +19127,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -19469,7 +19498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6317"/>
+  <dimension ref="A1:B6322"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -69991,15 +70020,55 @@
       <c r="A6315" t="s">
         <v>6344</v>
       </c>
+      <c r="B6315" s="1">
+        <v>4344.8830600000001</v>
+      </c>
     </row>
     <row r="6316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6316" t="s">
-        <v>6344</v>
+        <v>6345</v>
+      </c>
+      <c r="B6316" s="1">
+        <v>4362.7093199999999</v>
       </c>
     </row>
     <row r="6317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6317" t="s">
-        <v>6345</v>
+        <v>6346</v>
+      </c>
+      <c r="B6317" s="1">
+        <v>4394.6775600000001</v>
+      </c>
+    </row>
+    <row r="6318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6318" t="s">
+        <v>6347</v>
+      </c>
+      <c r="B6318" s="1">
+        <v>4394.6775600000001</v>
+      </c>
+    </row>
+    <row r="6319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6319" t="s">
+        <v>6348</v>
+      </c>
+      <c r="B6319" s="1">
+        <v>4400.1811100000004</v>
+      </c>
+    </row>
+    <row r="6320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6320" t="s">
+        <v>6349</v>
+      </c>
+    </row>
+    <row r="6321" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6321" t="s">
+        <v>6349</v>
+      </c>
+    </row>
+    <row r="6322" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6322" t="s">
+        <v>6350</v>
       </c>
     </row>
   </sheetData>
@@ -70022,19 +70091,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6346</v>
+        <v>6351</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6347</v>
+        <v>6352</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6348</v>
+        <v>6353</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6349</v>
+        <v>6354</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6350</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70045,13 +70114,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70062,13 +70131,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70079,13 +70148,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70096,13 +70165,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70113,13 +70182,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70130,13 +70199,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70147,13 +70216,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70164,13 +70233,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70181,13 +70250,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70198,13 +70267,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70215,13 +70284,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70232,13 +70301,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70249,13 +70318,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70266,13 +70335,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70283,13 +70352,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6351</v>
+        <v>6356</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6352</v>
+        <v>6357</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6353</v>
+        <v>6358</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B47B45-0502-4118-B239-311A04C3517F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DCBDBF-68D7-4EE6-80BA-B7DCABEB4B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,25 +11,12 @@
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
     <sheet name="Información" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6404" uniqueCount="6359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6406" uniqueCount="6361">
   <si>
     <t>Fecha</t>
   </si>
@@ -19078,10 +19065,16 @@
     <t>2026/03/09</t>
   </si>
   <si>
+    <t>2026/03/10</t>
+  </si>
+  <si>
+    <t>2026/03/11</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República martes, 10 de marzo de 2026 10:26:32 a. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 12 de marzo de 2026 8:33:53 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19127,7 +19120,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -19498,7 +19490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6322"/>
+  <dimension ref="A1:B6324"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70060,15 +70052,31 @@
       <c r="A6320" t="s">
         <v>6349</v>
       </c>
-    </row>
-    <row r="6321" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B6320" s="1">
+        <v>4361.6151399999999</v>
+      </c>
+    </row>
+    <row r="6321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6321" t="s">
-        <v>6349</v>
-      </c>
-    </row>
-    <row r="6322" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6350</v>
+      </c>
+      <c r="B6321" s="1">
+        <v>4291.74982</v>
+      </c>
+    </row>
+    <row r="6322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6322" t="s">
-        <v>6350</v>
+        <v>6351</v>
+      </c>
+    </row>
+    <row r="6323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6323" t="s">
+        <v>6351</v>
+      </c>
+    </row>
+    <row r="6324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6324" t="s">
+        <v>6352</v>
       </c>
     </row>
   </sheetData>
@@ -70091,19 +70099,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6351</v>
+        <v>6353</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6352</v>
+        <v>6354</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6353</v>
+        <v>6355</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6354</v>
+        <v>6356</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6355</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70114,13 +70122,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70131,13 +70139,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70148,13 +70156,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70165,13 +70173,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70182,13 +70190,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70199,13 +70207,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70216,13 +70224,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70233,13 +70241,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70250,13 +70258,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70267,13 +70275,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70284,13 +70292,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70301,13 +70309,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70318,13 +70326,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70335,13 +70343,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70352,13 +70360,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6356</v>
+        <v>6358</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6357</v>
+        <v>6359</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6358</v>
+        <v>6360</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52DCBDBF-68D7-4EE6-80BA-B7DCABEB4B6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA592A4-3691-40DC-8E05-995B9B8B3FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6406" uniqueCount="6361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6412" uniqueCount="6367">
   <si>
     <t>Fecha</t>
   </si>
@@ -19071,10 +19071,28 @@
     <t>2026/03/11</t>
   </si>
   <si>
+    <t>2026/03/12</t>
+  </si>
+  <si>
+    <t>2026/03/13</t>
+  </si>
+  <si>
+    <t>2026/03/14</t>
+  </si>
+  <si>
+    <t>2026/03/15</t>
+  </si>
+  <si>
+    <t>2026/03/16</t>
+  </si>
+  <si>
+    <t>2026/03/17</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 12 de marzo de 2026 8:33:53 a. m.</t>
+    <t>Descargado de sistema del Banco de la República martes, 17 de marzo de 2026 3:05:12 p. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19490,7 +19508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6324"/>
+  <dimension ref="A1:B6330"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70068,15 +70086,63 @@
       <c r="A6322" t="s">
         <v>6351</v>
       </c>
+      <c r="B6322" s="1">
+        <v>4249.3482000000004</v>
+      </c>
     </row>
     <row r="6323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6323" t="s">
-        <v>6351</v>
+        <v>6352</v>
+      </c>
+      <c r="B6323" s="1">
+        <v>4234.8064199999999</v>
       </c>
     </row>
     <row r="6324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6324" t="s">
-        <v>6352</v>
+        <v>6353</v>
+      </c>
+      <c r="B6324" s="1">
+        <v>4217.7205299999996</v>
+      </c>
+    </row>
+    <row r="6325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6325" t="s">
+        <v>6354</v>
+      </c>
+      <c r="B6325" s="1">
+        <v>4217.7205299999996</v>
+      </c>
+    </row>
+    <row r="6326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6326" t="s">
+        <v>6355</v>
+      </c>
+      <c r="B6326" s="1">
+        <v>4232.8311999999996</v>
+      </c>
+    </row>
+    <row r="6327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6327" t="s">
+        <v>6356</v>
+      </c>
+      <c r="B6327" s="1">
+        <v>4254.5455599999996</v>
+      </c>
+    </row>
+    <row r="6328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6328" t="s">
+        <v>6357</v>
+      </c>
+    </row>
+    <row r="6329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6329" t="s">
+        <v>6357</v>
+      </c>
+    </row>
+    <row r="6330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6330" t="s">
+        <v>6358</v>
       </c>
     </row>
   </sheetData>
@@ -70099,19 +70165,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6353</v>
+        <v>6359</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6354</v>
+        <v>6360</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6355</v>
+        <v>6361</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6356</v>
+        <v>6362</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6357</v>
+        <v>6363</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70122,13 +70188,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70139,13 +70205,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70156,13 +70222,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70173,13 +70239,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70190,13 +70256,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70207,13 +70273,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70224,13 +70290,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70241,13 +70307,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70258,13 +70324,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70275,13 +70341,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70292,13 +70358,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70309,13 +70375,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70326,13 +70392,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70343,13 +70409,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70360,13 +70426,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6358</v>
+        <v>6364</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6359</v>
+        <v>6365</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA592A4-3691-40DC-8E05-995B9B8B3FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F190D506-CBCB-4C63-A9E0-163147EFCE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19092,7 +19092,7 @@
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República martes, 17 de marzo de 2026 3:05:12 p. m.</t>
+    <t>Descargado de sistema del Banco de la República miércoles, 18 de marzo de 2026 8:49:17 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F190D506-CBCB-4C63-A9E0-163147EFCE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3502F45-66C9-4902-895B-C0CAE35FEF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6412" uniqueCount="6367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6413" uniqueCount="6368">
   <si>
     <t>Fecha</t>
   </si>
@@ -19089,10 +19089,13 @@
     <t>2026/03/17</t>
   </si>
   <si>
+    <t>2026/03/18</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República miércoles, 18 de marzo de 2026 8:49:17 a. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 19 de marzo de 2026 10:25:56 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19508,7 +19511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6330"/>
+  <dimension ref="A1:B6331"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70134,15 +70137,23 @@
       <c r="A6328" t="s">
         <v>6357</v>
       </c>
+      <c r="B6328" s="1">
+        <v>4248.0779599999996</v>
+      </c>
     </row>
     <row r="6329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6329" t="s">
-        <v>6357</v>
+        <v>6358</v>
       </c>
     </row>
     <row r="6330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6330" t="s">
         <v>6358</v>
+      </c>
+    </row>
+    <row r="6331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6331" t="s">
+        <v>6359</v>
       </c>
     </row>
   </sheetData>
@@ -70165,19 +70176,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6359</v>
+        <v>6360</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6360</v>
+        <v>6361</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6361</v>
+        <v>6362</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6362</v>
+        <v>6363</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6363</v>
+        <v>6364</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70188,13 +70199,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70205,13 +70216,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70222,13 +70233,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70239,13 +70250,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70256,13 +70267,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70273,13 +70284,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70290,13 +70301,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70307,13 +70318,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70324,13 +70335,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70341,13 +70352,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70358,13 +70369,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70375,13 +70386,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70392,13 +70403,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70409,13 +70420,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70426,13 +70437,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6365</v>
+        <v>6366</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6366</v>
+        <v>6367</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3502F45-66C9-4902-895B-C0CAE35FEF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E2555-4733-4A69-B3CF-8D346940D3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6413" uniqueCount="6368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6419" uniqueCount="6374">
   <si>
     <t>Fecha</t>
   </si>
@@ -19092,10 +19092,28 @@
     <t>2026/03/18</t>
   </si>
   <si>
+    <t>2026/03/19</t>
+  </si>
+  <si>
+    <t>2026/03/20</t>
+  </si>
+  <si>
+    <t>2026/03/21</t>
+  </si>
+  <si>
+    <t>2026/03/22</t>
+  </si>
+  <si>
+    <t>2026/03/23</t>
+  </si>
+  <si>
+    <t>2026/03/24</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 19 de marzo de 2026 10:25:56 a. m.</t>
+    <t>Descargado de sistema del Banco de la República miércoles, 25 de marzo de 2026 8:56:40 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19511,7 +19529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6331"/>
+  <dimension ref="A1:B6337"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70145,15 +70163,63 @@
       <c r="A6329" t="s">
         <v>6358</v>
       </c>
+      <c r="B6329" s="1">
+        <v>4264.79612</v>
+      </c>
     </row>
     <row r="6330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6330" t="s">
-        <v>6358</v>
+        <v>6359</v>
+      </c>
+      <c r="B6330" s="1">
+        <v>4262.9681600000004</v>
       </c>
     </row>
     <row r="6331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6331" t="s">
-        <v>6359</v>
+        <v>6360</v>
+      </c>
+      <c r="B6331" s="1">
+        <v>4277.2724099999996</v>
+      </c>
+    </row>
+    <row r="6332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6332" t="s">
+        <v>6361</v>
+      </c>
+      <c r="B6332" s="1">
+        <v>4277.2724099999996</v>
+      </c>
+    </row>
+    <row r="6333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6333" t="s">
+        <v>6362</v>
+      </c>
+      <c r="B6333" s="1">
+        <v>4292.2771300000004</v>
+      </c>
+    </row>
+    <row r="6334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6334" t="s">
+        <v>6363</v>
+      </c>
+      <c r="B6334" s="1">
+        <v>4289.4984800000002</v>
+      </c>
+    </row>
+    <row r="6335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6335" t="s">
+        <v>6364</v>
+      </c>
+    </row>
+    <row r="6336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6336" t="s">
+        <v>6364</v>
+      </c>
+    </row>
+    <row r="6337" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6337" t="s">
+        <v>6365</v>
       </c>
     </row>
   </sheetData>
@@ -70176,19 +70242,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6360</v>
+        <v>6366</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6361</v>
+        <v>6367</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6362</v>
+        <v>6368</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6363</v>
+        <v>6369</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6364</v>
+        <v>6370</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70199,13 +70265,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70216,13 +70282,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70233,13 +70299,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70250,13 +70316,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70267,13 +70333,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70284,13 +70350,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70301,13 +70367,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70318,13 +70384,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70335,13 +70401,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70352,13 +70418,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70369,13 +70435,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70386,13 +70452,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70403,13 +70469,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70420,13 +70486,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70437,13 +70503,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6365</v>
+        <v>6371</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6366</v>
+        <v>6372</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6367</v>
+        <v>6373</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0E2555-4733-4A69-B3CF-8D346940D3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2612BD6C-44BD-4113-9638-1A3D5588CDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6419" uniqueCount="6374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6424" uniqueCount="6379">
   <si>
     <t>Fecha</t>
   </si>
@@ -19110,10 +19110,25 @@
     <t>2026/03/24</t>
   </si>
   <si>
+    <t>2026/03/25</t>
+  </si>
+  <si>
+    <t>2026/03/26</t>
+  </si>
+  <si>
+    <t>2026/03/27</t>
+  </si>
+  <si>
+    <t>2026/03/28</t>
+  </si>
+  <si>
+    <t>2026/03/29</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República miércoles, 25 de marzo de 2026 8:56:40 a. m.</t>
+    <t>Descargado de sistema del Banco de la República lunes, 30 de marzo de 2026 7:58:22 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19529,7 +19544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6337"/>
+  <dimension ref="A1:B6342"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70211,15 +70226,55 @@
       <c r="A6335" t="s">
         <v>6364</v>
       </c>
+      <c r="B6335" s="1">
+        <v>4281.6751899999999</v>
+      </c>
     </row>
     <row r="6336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6336" t="s">
-        <v>6364</v>
-      </c>
-    </row>
-    <row r="6337" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6365</v>
+      </c>
+      <c r="B6336" s="1">
+        <v>4256.8516799999998</v>
+      </c>
+    </row>
+    <row r="6337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6337" t="s">
-        <v>6365</v>
+        <v>6366</v>
+      </c>
+      <c r="B6337" s="1">
+        <v>4234.1178399999999</v>
+      </c>
+    </row>
+    <row r="6338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6338" t="s">
+        <v>6367</v>
+      </c>
+      <c r="B6338" s="1">
+        <v>4226.7447199999997</v>
+      </c>
+    </row>
+    <row r="6339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6339" t="s">
+        <v>6368</v>
+      </c>
+      <c r="B6339" s="1">
+        <v>4226.7447199999997</v>
+      </c>
+    </row>
+    <row r="6340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6340" t="s">
+        <v>6369</v>
+      </c>
+    </row>
+    <row r="6341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6341" t="s">
+        <v>6369</v>
+      </c>
+    </row>
+    <row r="6342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6342" t="s">
+        <v>6370</v>
       </c>
     </row>
   </sheetData>
@@ -70242,19 +70297,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6366</v>
+        <v>6371</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6367</v>
+        <v>6372</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6368</v>
+        <v>6373</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6369</v>
+        <v>6374</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6370</v>
+        <v>6375</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70265,13 +70320,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70282,13 +70337,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70299,13 +70354,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70316,13 +70371,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70333,13 +70388,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70350,13 +70405,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70367,13 +70422,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70384,13 +70439,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70401,13 +70456,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70418,13 +70473,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70435,13 +70490,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70452,13 +70507,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70469,13 +70524,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70486,13 +70541,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70503,13 +70558,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6371</v>
+        <v>6376</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6372</v>
+        <v>6377</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6373</v>
+        <v>6378</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2612BD6C-44BD-4113-9638-1A3D5588CDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21F4056-0DF5-4D54-A292-BA2B1347A4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6424" uniqueCount="6379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6431" uniqueCount="6386">
   <si>
     <t>Fecha</t>
   </si>
@@ -19125,10 +19125,31 @@
     <t>2026/03/29</t>
   </si>
   <si>
+    <t>2026/03/30</t>
+  </si>
+  <si>
+    <t>2026/03/31</t>
+  </si>
+  <si>
+    <t>2026/04/01</t>
+  </si>
+  <si>
+    <t>2026/04/02</t>
+  </si>
+  <si>
+    <t>2026/04/03</t>
+  </si>
+  <si>
+    <t>2026/04/04</t>
+  </si>
+  <si>
+    <t>2026/04/05</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República lunes, 30 de marzo de 2026 7:58:22 a. m.</t>
+    <t>Descargado de sistema del Banco de la República lunes, 6 de abril de 2026 9:09:04 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19544,7 +19565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6342"/>
+  <dimension ref="A1:B6349"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70266,15 +70287,71 @@
       <c r="A6340" t="s">
         <v>6369</v>
       </c>
+      <c r="B6340" s="1">
+        <v>4206.5658199999998</v>
+      </c>
     </row>
     <row r="6341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6341" t="s">
-        <v>6369</v>
+        <v>6370</v>
+      </c>
+      <c r="B6341" s="1">
+        <v>4228.5279099999998</v>
       </c>
     </row>
     <row r="6342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6342" t="s">
-        <v>6370</v>
+        <v>6371</v>
+      </c>
+      <c r="B6342" s="1">
+        <v>4254.3172299999997</v>
+      </c>
+    </row>
+    <row r="6343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6343" t="s">
+        <v>6372</v>
+      </c>
+      <c r="B6343" s="1">
+        <v>4245.9281300000002</v>
+      </c>
+    </row>
+    <row r="6344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6344" t="s">
+        <v>6373</v>
+      </c>
+      <c r="B6344" s="1">
+        <v>4245.9281300000002</v>
+      </c>
+    </row>
+    <row r="6345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6345" t="s">
+        <v>6374</v>
+      </c>
+      <c r="B6345" s="1">
+        <v>4245.9281300000002</v>
+      </c>
+    </row>
+    <row r="6346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6346" t="s">
+        <v>6375</v>
+      </c>
+      <c r="B6346" s="1">
+        <v>4245.9281300000002</v>
+      </c>
+    </row>
+    <row r="6347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6347" t="s">
+        <v>6376</v>
+      </c>
+    </row>
+    <row r="6348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6348" t="s">
+        <v>6376</v>
+      </c>
+    </row>
+    <row r="6349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6349" t="s">
+        <v>6377</v>
       </c>
     </row>
   </sheetData>
@@ -70297,19 +70374,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6371</v>
+        <v>6378</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6372</v>
+        <v>6379</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6373</v>
+        <v>6380</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6374</v>
+        <v>6381</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6375</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70320,13 +70397,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70337,13 +70414,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70354,13 +70431,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70371,13 +70448,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70388,13 +70465,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70405,13 +70482,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70422,13 +70499,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70439,13 +70516,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70456,13 +70533,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70473,13 +70550,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70490,13 +70567,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70507,13 +70584,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70524,13 +70601,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70541,13 +70618,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70558,13 +70635,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6376</v>
+        <v>6383</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6377</v>
+        <v>6384</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6378</v>
+        <v>6385</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21F4056-0DF5-4D54-A292-BA2B1347A4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685474A1-A6B8-45B4-8A5A-F3E6A260365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6431" uniqueCount="6386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6434" uniqueCount="6389">
   <si>
     <t>Fecha</t>
   </si>
@@ -19146,10 +19146,19 @@
     <t>2026/04/05</t>
   </si>
   <si>
+    <t>2026/04/06</t>
+  </si>
+  <si>
+    <t>2026/04/07</t>
+  </si>
+  <si>
+    <t>2026/04/08</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República lunes, 6 de abril de 2026 9:09:04 a. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 9 de abril de 2026 8:38:59 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19565,7 +19574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6349"/>
+  <dimension ref="A1:B6352"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70343,15 +70352,39 @@
       <c r="A6347" t="s">
         <v>6376</v>
       </c>
+      <c r="B6347" s="1">
+        <v>4242.8036899999997</v>
+      </c>
     </row>
     <row r="6348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6348" t="s">
-        <v>6376</v>
+        <v>6377</v>
+      </c>
+      <c r="B6348" s="1">
+        <v>4240.8216899999998</v>
       </c>
     </row>
     <row r="6349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6349" t="s">
-        <v>6377</v>
+        <v>6378</v>
+      </c>
+      <c r="B6349" s="1">
+        <v>4301.6432000000004</v>
+      </c>
+    </row>
+    <row r="6350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6350" t="s">
+        <v>6379</v>
+      </c>
+    </row>
+    <row r="6351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6351" t="s">
+        <v>6379</v>
+      </c>
+    </row>
+    <row r="6352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6352" t="s">
+        <v>6380</v>
       </c>
     </row>
   </sheetData>
@@ -70374,19 +70407,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6378</v>
+        <v>6381</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6379</v>
+        <v>6382</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6380</v>
+        <v>6383</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6381</v>
+        <v>6384</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6382</v>
+        <v>6385</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70397,13 +70430,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70414,13 +70447,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70431,13 +70464,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70448,13 +70481,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70465,13 +70498,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70482,13 +70515,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70499,13 +70532,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70516,13 +70549,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70533,13 +70566,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70550,13 +70583,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70567,13 +70600,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70584,13 +70617,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70601,13 +70634,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70618,13 +70651,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70635,13 +70668,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6383</v>
+        <v>6386</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6384</v>
+        <v>6387</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6385</v>
+        <v>6388</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685474A1-A6B8-45B4-8A5A-F3E6A260365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2001BD6E-A047-42B5-A523-08EE0B5CC389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6434" uniqueCount="6389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6438" uniqueCount="6393">
   <si>
     <t>Fecha</t>
   </si>
@@ -19155,10 +19155,22 @@
     <t>2026/04/08</t>
   </si>
   <si>
+    <t>2026/04/09</t>
+  </si>
+  <si>
+    <t>2026/04/10</t>
+  </si>
+  <si>
+    <t>2026/04/11</t>
+  </si>
+  <si>
+    <t>2026/04/12</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 9 de abril de 2026 8:38:59 a. m.</t>
+    <t>Descargado de sistema del Banco de la República lunes, 13 de abril de 2026 8:35:46 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19574,7 +19586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6352"/>
+  <dimension ref="A1:B6356"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70376,15 +70388,47 @@
       <c r="A6350" t="s">
         <v>6379</v>
       </c>
+      <c r="B6350" s="1">
+        <v>4253.8941199999999</v>
+      </c>
     </row>
     <row r="6351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6351" t="s">
-        <v>6379</v>
+        <v>6380</v>
+      </c>
+      <c r="B6351" s="1">
+        <v>4272.6104500000001</v>
       </c>
     </row>
     <row r="6352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6352" t="s">
-        <v>6380</v>
+        <v>6381</v>
+      </c>
+      <c r="B6352" s="1">
+        <v>4259.1930400000001</v>
+      </c>
+    </row>
+    <row r="6353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6353" t="s">
+        <v>6382</v>
+      </c>
+      <c r="B6353" s="1">
+        <v>4259.1930400000001</v>
+      </c>
+    </row>
+    <row r="6354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6354" t="s">
+        <v>6383</v>
+      </c>
+    </row>
+    <row r="6355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6355" t="s">
+        <v>6383</v>
+      </c>
+    </row>
+    <row r="6356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6356" t="s">
+        <v>6384</v>
       </c>
     </row>
   </sheetData>
@@ -70407,19 +70451,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6381</v>
+        <v>6385</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6382</v>
+        <v>6386</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6383</v>
+        <v>6387</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6384</v>
+        <v>6388</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6385</v>
+        <v>6389</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70430,13 +70474,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70447,13 +70491,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70464,13 +70508,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70481,13 +70525,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70498,13 +70542,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70515,13 +70559,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70532,13 +70576,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70549,13 +70593,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70566,13 +70610,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70583,13 +70627,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70600,13 +70644,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70617,13 +70661,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70634,13 +70678,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70651,13 +70695,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70668,13 +70712,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6386</v>
+        <v>6390</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6387</v>
+        <v>6391</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6388</v>
+        <v>6392</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2001BD6E-A047-42B5-A523-08EE0B5CC389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD91E2B5-1E1D-4A8D-917B-101F92A1B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6438" uniqueCount="6393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6439" uniqueCount="6394">
   <si>
     <t>Fecha</t>
   </si>
@@ -19167,10 +19167,13 @@
     <t>2026/04/12</t>
   </si>
   <si>
+    <t>2026/04/13</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República lunes, 13 de abril de 2026 8:35:46 a. m.</t>
+    <t>Descargado de sistema del Banco de la República martes, 14 de abril de 2026 9:00:30 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19586,7 +19589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6356"/>
+  <dimension ref="A1:B6357"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70420,15 +70423,23 @@
       <c r="A6354" t="s">
         <v>6383</v>
       </c>
+      <c r="B6354" s="1">
+        <v>4252.6563599999999</v>
+      </c>
     </row>
     <row r="6355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6355" t="s">
-        <v>6383</v>
+        <v>6384</v>
       </c>
     </row>
     <row r="6356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6356" t="s">
         <v>6384</v>
+      </c>
+    </row>
+    <row r="6357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6357" t="s">
+        <v>6385</v>
       </c>
     </row>
   </sheetData>
@@ -70451,19 +70462,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6385</v>
+        <v>6386</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6386</v>
+        <v>6387</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6387</v>
+        <v>6388</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6388</v>
+        <v>6389</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6389</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70474,13 +70485,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70491,13 +70502,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70508,13 +70519,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70525,13 +70536,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70542,13 +70553,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70559,13 +70570,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70576,13 +70587,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70593,13 +70604,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70610,13 +70621,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70627,13 +70638,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70644,13 +70655,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70661,13 +70672,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70678,13 +70689,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70695,13 +70706,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70712,13 +70723,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6390</v>
+        <v>6391</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6391</v>
+        <v>6392</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6392</v>
+        <v>6393</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004B080E-BCC0-4F82-8D3D-D64AD79FAEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736F4380-1D57-4C3F-8CC7-79F772A84DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6452" uniqueCount="6407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6476" uniqueCount="6431">
   <si>
     <t>Fecha</t>
   </si>
@@ -19209,10 +19209,82 @@
     <t>2026/04/26</t>
   </si>
   <si>
+    <t>2026/04/27</t>
+  </si>
+  <si>
+    <t>2026/04/28</t>
+  </si>
+  <si>
+    <t>2026/04/29</t>
+  </si>
+  <si>
+    <t>2026/04/30</t>
+  </si>
+  <si>
+    <t>2026/05/01</t>
+  </si>
+  <si>
+    <t>2026/05/02</t>
+  </si>
+  <si>
+    <t>2026/05/03</t>
+  </si>
+  <si>
+    <t>2026/05/04</t>
+  </si>
+  <si>
+    <t>2026/05/05</t>
+  </si>
+  <si>
+    <t>2026/05/06</t>
+  </si>
+  <si>
+    <t>2026/05/07</t>
+  </si>
+  <si>
+    <t>2026/05/08</t>
+  </si>
+  <si>
+    <t>2026/05/09</t>
+  </si>
+  <si>
+    <t>2026/05/10</t>
+  </si>
+  <si>
+    <t>2026/05/11</t>
+  </si>
+  <si>
+    <t>2026/05/12</t>
+  </si>
+  <si>
+    <t>2026/05/13</t>
+  </si>
+  <si>
+    <t>2026/05/14</t>
+  </si>
+  <si>
+    <t>2026/05/15</t>
+  </si>
+  <si>
+    <t>2026/05/16</t>
+  </si>
+  <si>
+    <t>2026/05/17</t>
+  </si>
+  <si>
+    <t>2026/05/18</t>
+  </si>
+  <si>
+    <t>2026/05/19</t>
+  </si>
+  <si>
+    <t>2026/05/20</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República lunes, 27 de abril de 2026 8:02:10 a. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 21 de mayo de 2026 10:59:10 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19628,7 +19700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6370"/>
+  <dimension ref="A1:B6394"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70574,15 +70646,207 @@
       <c r="A6368" t="s">
         <v>6397</v>
       </c>
-    </row>
-    <row r="6369" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B6368" s="1">
+        <v>4167.6531100000002</v>
+      </c>
+    </row>
+    <row r="6369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6369" t="s">
-        <v>6397</v>
-      </c>
-    </row>
-    <row r="6370" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6398</v>
+      </c>
+      <c r="B6369" s="1">
+        <v>4204.7275300000001</v>
+      </c>
+    </row>
+    <row r="6370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6370" t="s">
-        <v>6398</v>
+        <v>6399</v>
+      </c>
+      <c r="B6370" s="1">
+        <v>4251.4992000000002</v>
+      </c>
+    </row>
+    <row r="6371" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6371" t="s">
+        <v>6400</v>
+      </c>
+      <c r="B6371" s="1">
+        <v>4248.6228700000001</v>
+      </c>
+    </row>
+    <row r="6372" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6372" t="s">
+        <v>6401</v>
+      </c>
+      <c r="B6372" s="1">
+        <v>4280.4398899999997</v>
+      </c>
+    </row>
+    <row r="6373" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6373" t="s">
+        <v>6402</v>
+      </c>
+      <c r="B6373" s="1">
+        <v>4280.4398899999997</v>
+      </c>
+    </row>
+    <row r="6374" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6374" t="s">
+        <v>6403</v>
+      </c>
+      <c r="B6374" s="1">
+        <v>4280.4398899999997</v>
+      </c>
+    </row>
+    <row r="6375" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6375" t="s">
+        <v>6404</v>
+      </c>
+      <c r="B6375" s="1">
+        <v>4258.7966999999999</v>
+      </c>
+    </row>
+    <row r="6376" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6376" t="s">
+        <v>6405</v>
+      </c>
+      <c r="B6376" s="1">
+        <v>4339.9077600000001</v>
+      </c>
+    </row>
+    <row r="6377" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6377" t="s">
+        <v>6406</v>
+      </c>
+      <c r="B6377" s="1">
+        <v>4377.3329100000001</v>
+      </c>
+    </row>
+    <row r="6378" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6378" t="s">
+        <v>6407</v>
+      </c>
+      <c r="B6378" s="1">
+        <v>4365.07438</v>
+      </c>
+    </row>
+    <row r="6379" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6379" t="s">
+        <v>6408</v>
+      </c>
+      <c r="B6379" s="1">
+        <v>4391.2154200000004</v>
+      </c>
+    </row>
+    <row r="6380" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6380" t="s">
+        <v>6409</v>
+      </c>
+      <c r="B6380" s="1">
+        <v>4412.2102500000001</v>
+      </c>
+    </row>
+    <row r="6381" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6381" t="s">
+        <v>6410</v>
+      </c>
+      <c r="B6381" s="1">
+        <v>4412.2102500000001</v>
+      </c>
+    </row>
+    <row r="6382" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6382" t="s">
+        <v>6411</v>
+      </c>
+      <c r="B6382" s="1">
+        <v>4414.0838000000003</v>
+      </c>
+    </row>
+    <row r="6383" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6383" t="s">
+        <v>6412</v>
+      </c>
+      <c r="B6383" s="1">
+        <v>4411.3744500000003</v>
+      </c>
+    </row>
+    <row r="6384" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6384" t="s">
+        <v>6413</v>
+      </c>
+      <c r="B6384" s="1">
+        <v>4420.0406999999996</v>
+      </c>
+    </row>
+    <row r="6385" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6385" t="s">
+        <v>6414</v>
+      </c>
+      <c r="B6385" s="1">
+        <v>4432.4548800000002</v>
+      </c>
+    </row>
+    <row r="6386" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6386" t="s">
+        <v>6415</v>
+      </c>
+      <c r="B6386" s="1">
+        <v>4401.6061</v>
+      </c>
+    </row>
+    <row r="6387" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6387" t="s">
+        <v>6416</v>
+      </c>
+      <c r="B6387" s="1">
+        <v>4415.6551399999998</v>
+      </c>
+    </row>
+    <row r="6388" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6388" t="s">
+        <v>6417</v>
+      </c>
+      <c r="B6388" s="1">
+        <v>4415.6551399999998</v>
+      </c>
+    </row>
+    <row r="6389" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6389" t="s">
+        <v>6418</v>
+      </c>
+      <c r="B6389" s="1">
+        <v>4420.2112699999998</v>
+      </c>
+    </row>
+    <row r="6390" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6390" t="s">
+        <v>6419</v>
+      </c>
+      <c r="B6390" s="1">
+        <v>4402.9359199999999</v>
+      </c>
+    </row>
+    <row r="6391" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6391" t="s">
+        <v>6420</v>
+      </c>
+      <c r="B6391" s="1">
+        <v>4411.9629400000003</v>
+      </c>
+    </row>
+    <row r="6392" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6392" t="s">
+        <v>6421</v>
+      </c>
+    </row>
+    <row r="6393" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6393" t="s">
+        <v>6421</v>
+      </c>
+    </row>
+    <row r="6394" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6394" t="s">
+        <v>6422</v>
       </c>
     </row>
   </sheetData>
@@ -70605,19 +70869,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6399</v>
+        <v>6423</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6400</v>
+        <v>6424</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6401</v>
+        <v>6425</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6402</v>
+        <v>6426</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6403</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70628,13 +70892,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70645,13 +70909,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70662,13 +70926,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70679,13 +70943,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70696,13 +70960,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70713,13 +70977,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70730,13 +70994,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70747,13 +71011,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70764,13 +71028,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70781,13 +71045,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70798,13 +71062,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70815,13 +71079,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70832,13 +71096,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70849,13 +71113,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70866,13 +71130,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6404</v>
+        <v>6428</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6405</v>
+        <v>6429</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6406</v>
+        <v>6430</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736F4380-1D57-4C3F-8CC7-79F772A84DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D526D9-6943-4938-B9D9-07C9D4D0D657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6476" uniqueCount="6431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6481" uniqueCount="6436">
   <si>
     <t>Fecha</t>
   </si>
@@ -19281,10 +19281,25 @@
     <t>2026/05/20</t>
   </si>
   <si>
+    <t>2026/05/21</t>
+  </si>
+  <si>
+    <t>2026/05/22</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>2026/05/24</t>
+  </si>
+  <si>
+    <t>2026/05/25</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 21 de mayo de 2026 10:59:10 a. m.</t>
+    <t>Descargado de sistema del Banco de la República martes, 26 de mayo de 2026 8:13:31 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19700,7 +19715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6394"/>
+  <dimension ref="A1:B6399"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -70838,15 +70853,55 @@
       <c r="A6392" t="s">
         <v>6421</v>
       </c>
+      <c r="B6392" s="1">
+        <v>4324.9435800000001</v>
+      </c>
     </row>
     <row r="6393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6393" t="s">
-        <v>6421</v>
+        <v>6422</v>
+      </c>
+      <c r="B6393" s="1">
+        <v>4292.8489200000004</v>
       </c>
     </row>
     <row r="6394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6394" t="s">
-        <v>6422</v>
+        <v>6423</v>
+      </c>
+      <c r="B6394" s="1">
+        <v>4253.0561799999996</v>
+      </c>
+    </row>
+    <row r="6395" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6395" t="s">
+        <v>6424</v>
+      </c>
+      <c r="B6395" s="1">
+        <v>4253.0561799999996</v>
+      </c>
+    </row>
+    <row r="6396" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6396" t="s">
+        <v>6425</v>
+      </c>
+      <c r="B6396" s="1">
+        <v>4269.1912499999999</v>
+      </c>
+    </row>
+    <row r="6397" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6397" t="s">
+        <v>6426</v>
+      </c>
+    </row>
+    <row r="6398" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6398" t="s">
+        <v>6426</v>
+      </c>
+    </row>
+    <row r="6399" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6399" t="s">
+        <v>6427</v>
       </c>
     </row>
   </sheetData>
@@ -70869,19 +70924,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6423</v>
+        <v>6428</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6424</v>
+        <v>6429</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6425</v>
+        <v>6430</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6426</v>
+        <v>6431</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6427</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70892,13 +70947,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70909,13 +70964,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70926,13 +70981,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70943,13 +70998,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70960,13 +71015,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70977,13 +71032,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -70994,13 +71049,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71011,13 +71066,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71028,13 +71083,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71045,13 +71100,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71062,13 +71117,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71079,13 +71134,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71096,13 +71151,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71113,13 +71168,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71130,13 +71185,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6428</v>
+        <v>6433</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6429</v>
+        <v>6434</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6430</v>
+        <v>6435</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6397"/>
+  <dimension ref="A1:B6400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64391,6 +64391,36 @@
         <v>4237.24304</v>
       </c>
     </row>
+    <row r="6398">
+      <c r="A6398" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B6398" s="1" t="n">
+        <v>4229.87115</v>
+      </c>
+    </row>
+    <row r="6399">
+      <c r="A6399" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B6399" s="1" t="n">
+        <v>4255.37653</v>
+      </c>
+    </row>
+    <row r="6400">
+      <c r="A6400" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B6400" s="1" t="n">
+        <v>4292.21714</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B39466-3CE5-40A4-B1B7-9C7B55AC5C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B567F89-4DC6-48E7-978F-9961AC8D188D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6494" uniqueCount="6449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6497" uniqueCount="6452">
   <si>
     <t>Fecha</t>
   </si>
@@ -19335,10 +19335,19 @@
     <t>2026/06/07</t>
   </si>
   <si>
+    <t>2026/06/08</t>
+  </si>
+  <si>
+    <t>2026/06/09</t>
+  </si>
+  <si>
+    <t>2026/06/10</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República lunes, 8 de junio de 2026 9:44:53 a. m.</t>
+    <t>Descargado de sistema del Banco de la República miércoles, 10 de junio de 2026 3:05:41 p. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19754,7 +19763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6412"/>
+  <dimension ref="A1:B6415"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71036,15 +71045,39 @@
       <c r="A6410" t="s">
         <v>6439</v>
       </c>
+      <c r="B6410" s="1">
+        <v>4141.3734700000005</v>
+      </c>
     </row>
     <row r="6411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6411" t="s">
-        <v>6439</v>
+        <v>6440</v>
+      </c>
+      <c r="B6411" s="1">
+        <v>4148.5496499999999</v>
       </c>
     </row>
     <row r="6412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6412" t="s">
-        <v>6440</v>
+        <v>6441</v>
+      </c>
+      <c r="B6412" s="1">
+        <v>4137.4816600000004</v>
+      </c>
+    </row>
+    <row r="6413" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6413" t="s">
+        <v>6442</v>
+      </c>
+    </row>
+    <row r="6414" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6414" t="s">
+        <v>6442</v>
+      </c>
+    </row>
+    <row r="6415" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6415" t="s">
+        <v>6443</v>
       </c>
     </row>
   </sheetData>
@@ -71067,19 +71100,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6441</v>
+        <v>6444</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6442</v>
+        <v>6445</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6443</v>
+        <v>6446</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6444</v>
+        <v>6447</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6445</v>
+        <v>6448</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71090,13 +71123,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71107,13 +71140,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71124,13 +71157,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71141,13 +71174,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71158,13 +71191,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71175,13 +71208,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71192,13 +71225,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71209,13 +71242,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71226,13 +71259,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71243,13 +71276,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71260,13 +71293,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71277,13 +71310,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71294,13 +71327,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71311,13 +71344,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71328,13 +71361,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B567F89-4DC6-48E7-978F-9961AC8D188D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A37C51-64C4-4065-86D2-A71CF088AEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19347,7 +19347,7 @@
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República miércoles, 10 de junio de 2026 3:05:41 p. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 11 de junio de 2026 9:04:06 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A37C51-64C4-4065-86D2-A71CF088AEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E2F9CA-926E-47E1-9DC5-B8245A0FCF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6497" uniqueCount="6452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6498" uniqueCount="6453">
   <si>
     <t>Fecha</t>
   </si>
@@ -19344,10 +19344,13 @@
     <t>2026/06/10</t>
   </si>
   <si>
+    <t>2026/06/11</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 11 de junio de 2026 9:04:06 a. m.</t>
+    <t>Descargado de sistema del Banco de la República viernes, 12 de junio de 2026 9:47:06 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19763,7 +19766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6415"/>
+  <dimension ref="A1:B6416"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71069,15 +71072,23 @@
       <c r="A6413" t="s">
         <v>6442</v>
       </c>
+      <c r="B6413" s="1">
+        <v>4108.5972899999997</v>
+      </c>
     </row>
     <row r="6414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6414" t="s">
-        <v>6442</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="6415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6415" t="s">
         <v>6443</v>
+      </c>
+    </row>
+    <row r="6416" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6416" t="s">
+        <v>6444</v>
       </c>
     </row>
   </sheetData>
@@ -71100,19 +71111,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6444</v>
+        <v>6445</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6445</v>
+        <v>6446</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6446</v>
+        <v>6447</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6447</v>
+        <v>6448</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6448</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71123,13 +71134,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71140,13 +71151,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71157,13 +71168,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71174,13 +71185,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71191,13 +71202,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71208,13 +71219,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71225,13 +71236,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71242,13 +71253,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71259,13 +71270,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71276,13 +71287,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71293,13 +71304,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71310,13 +71321,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71327,13 +71338,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71344,13 +71355,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71361,13 +71372,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E2F9CA-926E-47E1-9DC5-B8245A0FCF00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4847B83C-B68E-4660-9401-04A4AD5A2E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6498" uniqueCount="6453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6501" uniqueCount="6456">
   <si>
     <t>Fecha</t>
   </si>
@@ -19347,10 +19347,19 @@
     <t>2026/06/11</t>
   </si>
   <si>
+    <t>2026/06/12</t>
+  </si>
+  <si>
+    <t>2026/06/13</t>
+  </si>
+  <si>
+    <t>2026/06/14</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República viernes, 12 de junio de 2026 9:47:06 a. m.</t>
+    <t>Descargado de sistema del Banco de la República lunes, 15 de junio de 2026 9:29:36 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19766,7 +19775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6416"/>
+  <dimension ref="A1:B6419"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71080,15 +71089,39 @@
       <c r="A6414" t="s">
         <v>6443</v>
       </c>
+      <c r="B6414" s="1">
+        <v>4066.7468699999999</v>
+      </c>
     </row>
     <row r="6415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6415" t="s">
-        <v>6443</v>
+        <v>6444</v>
+      </c>
+      <c r="B6415" s="1">
+        <v>4022.9721100000002</v>
       </c>
     </row>
     <row r="6416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6416" t="s">
-        <v>6444</v>
+        <v>6445</v>
+      </c>
+      <c r="B6416" s="1">
+        <v>4022.9721100000002</v>
+      </c>
+    </row>
+    <row r="6417" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6417" t="s">
+        <v>6446</v>
+      </c>
+    </row>
+    <row r="6418" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6418" t="s">
+        <v>6446</v>
+      </c>
+    </row>
+    <row r="6419" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6419" t="s">
+        <v>6447</v>
       </c>
     </row>
   </sheetData>
@@ -71111,19 +71144,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6445</v>
+        <v>6448</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6446</v>
+        <v>6449</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6447</v>
+        <v>6450</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6448</v>
+        <v>6451</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6449</v>
+        <v>6452</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71134,13 +71167,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71151,13 +71184,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71168,13 +71201,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71185,13 +71218,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71202,13 +71235,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71219,13 +71252,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71236,13 +71269,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71253,13 +71286,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71270,13 +71303,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71287,13 +71320,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71304,13 +71337,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71321,13 +71354,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71338,13 +71371,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71355,13 +71388,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71372,13 +71405,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6451</v>
+        <v>6454</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6452</v>
+        <v>6455</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4847B83C-B68E-4660-9401-04A4AD5A2E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D4783F-CC4E-44DC-BF56-11D5A5AED419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6501" uniqueCount="6456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6503" uniqueCount="6458">
   <si>
     <t>Fecha</t>
   </si>
@@ -19356,10 +19356,16 @@
     <t>2026/06/14</t>
   </si>
   <si>
+    <t>2026/06/15</t>
+  </si>
+  <si>
+    <t>2026/06/16</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República lunes, 15 de junio de 2026 9:29:36 a. m.</t>
+    <t>Descargado de sistema del Banco de la República miércoles, 17 de junio de 2026 10:43:20 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19775,7 +19781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6419"/>
+  <dimension ref="A1:B6421"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71109,19 +71115,35 @@
         <v>4022.9721100000002</v>
       </c>
     </row>
-    <row r="6417" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6417" t="s">
         <v>6446</v>
       </c>
-    </row>
-    <row r="6418" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B6417" s="1">
+        <v>4034.4419899999998</v>
+      </c>
+    </row>
+    <row r="6418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6418" t="s">
-        <v>6446</v>
-      </c>
-    </row>
-    <row r="6419" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6447</v>
+      </c>
+      <c r="B6418" s="1">
+        <v>4034.4419899999998</v>
+      </c>
+    </row>
+    <row r="6419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6419" t="s">
-        <v>6447</v>
+        <v>6448</v>
+      </c>
+    </row>
+    <row r="6420" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6420" t="s">
+        <v>6448</v>
+      </c>
+    </row>
+    <row r="6421" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6421" t="s">
+        <v>6449</v>
       </c>
     </row>
   </sheetData>
@@ -71144,19 +71166,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6448</v>
+        <v>6450</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6449</v>
+        <v>6451</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6450</v>
+        <v>6452</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6451</v>
+        <v>6453</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6452</v>
+        <v>6454</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71167,13 +71189,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71184,13 +71206,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71201,13 +71223,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71218,13 +71240,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71235,13 +71257,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71252,13 +71274,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71269,13 +71291,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71286,13 +71308,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71303,13 +71325,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71320,13 +71342,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71337,13 +71359,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71354,13 +71376,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71371,13 +71393,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71388,13 +71410,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71405,13 +71427,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6453</v>
+        <v>6455</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6454</v>
+        <v>6456</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6455</v>
+        <v>6457</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D4783F-CC4E-44DC-BF56-11D5A5AED419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B83217-3B08-4261-A0A5-61B4059F8075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6503" uniqueCount="6458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6504" uniqueCount="6459">
   <si>
     <t>Fecha</t>
   </si>
@@ -19362,10 +19362,13 @@
     <t>2026/06/16</t>
   </si>
   <si>
+    <t>2026/06/17</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República miércoles, 17 de junio de 2026 10:43:20 a. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 18 de junio de 2026 8:28:27 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19781,7 +19784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6421"/>
+  <dimension ref="A1:B6422"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71135,15 +71138,23 @@
       <c r="A6419" t="s">
         <v>6448</v>
       </c>
+      <c r="B6419" s="1">
+        <v>3971.8027699999998</v>
+      </c>
     </row>
     <row r="6420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6420" t="s">
-        <v>6448</v>
+        <v>6449</v>
       </c>
     </row>
     <row r="6421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6421" t="s">
         <v>6449</v>
+      </c>
+    </row>
+    <row r="6422" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6422" t="s">
+        <v>6450</v>
       </c>
     </row>
   </sheetData>
@@ -71166,19 +71177,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6450</v>
+        <v>6451</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6451</v>
+        <v>6452</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6452</v>
+        <v>6453</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6453</v>
+        <v>6454</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6454</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71189,13 +71200,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71206,13 +71217,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71223,13 +71234,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71240,13 +71251,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71257,13 +71268,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71274,13 +71285,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71291,13 +71302,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71308,13 +71319,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71325,13 +71336,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71342,13 +71353,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71359,13 +71370,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71376,13 +71387,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71393,13 +71404,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71410,13 +71421,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71427,13 +71438,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6455</v>
+        <v>6456</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B83217-3B08-4261-A0A5-61B4059F8075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1C677A-1E9E-4618-9490-4F01456147F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6504" uniqueCount="6459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6509" uniqueCount="6464">
   <si>
     <t>Fecha</t>
   </si>
@@ -19365,10 +19365,25 @@
     <t>2026/06/17</t>
   </si>
   <si>
+    <t>2026/06/18</t>
+  </si>
+  <si>
+    <t>2026/06/19</t>
+  </si>
+  <si>
+    <t>2026/06/20</t>
+  </si>
+  <si>
+    <t>2026/06/21</t>
+  </si>
+  <si>
+    <t>2026/06/22</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 18 de junio de 2026 8:28:27 a. m.</t>
+    <t>Descargado de sistema del Banco de la República martes, 23 de junio de 2026 7:35:28 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19784,7 +19799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6422"/>
+  <dimension ref="A1:B6427"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71146,15 +71161,55 @@
       <c r="A6420" t="s">
         <v>6449</v>
       </c>
+      <c r="B6420" s="1">
+        <v>3951.0806200000002</v>
+      </c>
     </row>
     <row r="6421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6421" t="s">
-        <v>6449</v>
+        <v>6450</v>
+      </c>
+      <c r="B6421" s="1">
+        <v>3967.9079299999999</v>
       </c>
     </row>
     <row r="6422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6422" t="s">
-        <v>6450</v>
+        <v>6451</v>
+      </c>
+      <c r="B6422" s="1">
+        <v>3967.9079299999999</v>
+      </c>
+    </row>
+    <row r="6423" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6423" t="s">
+        <v>6452</v>
+      </c>
+      <c r="B6423" s="1">
+        <v>3967.9079299999999</v>
+      </c>
+    </row>
+    <row r="6424" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6424" t="s">
+        <v>6453</v>
+      </c>
+      <c r="B6424" s="1">
+        <v>3959.6050599999999</v>
+      </c>
+    </row>
+    <row r="6425" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6425" t="s">
+        <v>6454</v>
+      </c>
+    </row>
+    <row r="6426" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6426" t="s">
+        <v>6454</v>
+      </c>
+    </row>
+    <row r="6427" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6427" t="s">
+        <v>6455</v>
       </c>
     </row>
   </sheetData>
@@ -71177,19 +71232,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6451</v>
+        <v>6456</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6452</v>
+        <v>6457</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6454</v>
+        <v>6459</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6455</v>
+        <v>6460</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71200,13 +71255,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71217,13 +71272,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71234,13 +71289,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71251,13 +71306,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71268,13 +71323,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71285,13 +71340,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71302,13 +71357,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71319,13 +71374,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71336,13 +71391,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71353,13 +71408,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71370,13 +71425,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71387,13 +71442,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71404,13 +71459,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71421,13 +71476,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71438,13 +71493,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6457</v>
+        <v>6462</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6458</v>
+        <v>6463</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1C677A-1E9E-4618-9490-4F01456147F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40C53EC-DD07-4A7A-8E58-33E4DE17B1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6509" uniqueCount="6464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6510" uniqueCount="6465">
   <si>
     <t>Fecha</t>
   </si>
@@ -19380,10 +19380,13 @@
     <t>2026/06/22</t>
   </si>
   <si>
+    <t>2026/06/23</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República martes, 23 de junio de 2026 7:35:28 a. m.</t>
+    <t>Descargado de sistema del Banco de la República miércoles, 24 de junio de 2026 7:57:23 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19799,7 +19802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6427"/>
+  <dimension ref="A1:B6428"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71201,15 +71204,23 @@
       <c r="A6425" t="s">
         <v>6454</v>
       </c>
+      <c r="B6425" s="1">
+        <v>3877.0388499999999</v>
+      </c>
     </row>
     <row r="6426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6426" t="s">
-        <v>6454</v>
+        <v>6455</v>
       </c>
     </row>
     <row r="6427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6427" t="s">
         <v>6455</v>
+      </c>
+    </row>
+    <row r="6428" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6428" t="s">
+        <v>6456</v>
       </c>
     </row>
   </sheetData>
@@ -71232,19 +71243,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6456</v>
+        <v>6457</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6457</v>
+        <v>6458</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6459</v>
+        <v>6460</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6460</v>
+        <v>6461</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71255,13 +71266,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71272,13 +71283,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71289,13 +71300,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71306,13 +71317,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71323,13 +71334,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71340,13 +71351,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71357,13 +71368,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71374,13 +71385,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71391,13 +71402,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71408,13 +71419,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71425,13 +71436,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71442,13 +71453,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71459,13 +71470,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71476,13 +71487,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71493,13 +71504,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6463</v>
+        <v>6464</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40C53EC-DD07-4A7A-8E58-33E4DE17B1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94BE1B4-BD1C-49D7-B0E6-43222C1972A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6510" uniqueCount="6465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6517" uniqueCount="6472">
   <si>
     <t>Fecha</t>
   </si>
@@ -19383,10 +19383,31 @@
     <t>2026/06/23</t>
   </si>
   <si>
+    <t>2026/06/24</t>
+  </si>
+  <si>
+    <t>2026/06/25</t>
+  </si>
+  <si>
+    <t>2026/06/26</t>
+  </si>
+  <si>
+    <t>2026/06/27</t>
+  </si>
+  <si>
+    <t>2026/06/28</t>
+  </si>
+  <si>
+    <t>2026/06/29</t>
+  </si>
+  <si>
+    <t>2026/06/30</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República miércoles, 24 de junio de 2026 7:57:23 a. m.</t>
+    <t>Descargado de sistema del Banco de la República miércoles, 1 de julio de 2026 9:30:26 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19802,7 +19823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6428"/>
+  <dimension ref="A1:B6435"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71212,15 +71233,71 @@
       <c r="A6426" t="s">
         <v>6455</v>
       </c>
+      <c r="B6426" s="1">
+        <v>3885.3698899999999</v>
+      </c>
     </row>
     <row r="6427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6427" t="s">
-        <v>6455</v>
+        <v>6456</v>
+      </c>
+      <c r="B6427" s="1">
+        <v>3900.2282399999999</v>
       </c>
     </row>
     <row r="6428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6428" t="s">
-        <v>6456</v>
+        <v>6457</v>
+      </c>
+      <c r="B6428" s="1">
+        <v>3912.71254</v>
+      </c>
+    </row>
+    <row r="6429" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6429" t="s">
+        <v>6458</v>
+      </c>
+      <c r="B6429" s="1">
+        <v>3923.9708000000001</v>
+      </c>
+    </row>
+    <row r="6430" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6430" t="s">
+        <v>6459</v>
+      </c>
+      <c r="B6430" s="1">
+        <v>3923.9708000000001</v>
+      </c>
+    </row>
+    <row r="6431" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6431" t="s">
+        <v>6460</v>
+      </c>
+      <c r="B6431" s="1">
+        <v>3933.44067</v>
+      </c>
+    </row>
+    <row r="6432" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6432" t="s">
+        <v>6461</v>
+      </c>
+      <c r="B6432" s="1">
+        <v>3937.0564399999998</v>
+      </c>
+    </row>
+    <row r="6433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6433" t="s">
+        <v>6462</v>
+      </c>
+    </row>
+    <row r="6434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6434" t="s">
+        <v>6462</v>
+      </c>
+    </row>
+    <row r="6435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6435" t="s">
+        <v>6463</v>
       </c>
     </row>
   </sheetData>
@@ -71243,19 +71320,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6457</v>
+        <v>6464</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6458</v>
+        <v>6465</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6459</v>
+        <v>6466</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6460</v>
+        <v>6467</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6461</v>
+        <v>6468</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71266,13 +71343,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71283,13 +71360,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71300,13 +71377,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71317,13 +71394,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71334,13 +71411,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71351,13 +71428,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71368,13 +71445,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71385,13 +71462,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71402,13 +71479,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71419,13 +71496,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71436,13 +71513,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71453,13 +71530,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71470,13 +71547,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71487,13 +71564,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71504,13 +71581,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6462</v>
+        <v>6469</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6463</v>
+        <v>6470</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6464</v>
+        <v>6471</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94BE1B4-BD1C-49D7-B0E6-43222C1972A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEEDFCF4-5D84-4C01-8175-89496F7770B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6517" uniqueCount="6472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6519" uniqueCount="6474">
   <si>
     <t>Fecha</t>
   </si>
@@ -19404,10 +19404,16 @@
     <t>2026/06/30</t>
   </si>
   <si>
+    <t>2026/07/01</t>
+  </si>
+  <si>
+    <t>2026/07/02</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República miércoles, 1 de julio de 2026 9:30:26 a. m.</t>
+    <t>Descargado de sistema del Banco de la República viernes, 3 de julio de 2026 8:13:43 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19823,7 +19829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6435"/>
+  <dimension ref="A1:B6437"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71285,19 +71291,35 @@
         <v>3937.0564399999998</v>
       </c>
     </row>
-    <row r="6433" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6433" t="s">
         <v>6462</v>
       </c>
-    </row>
-    <row r="6434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B6433" s="1">
+        <v>3920.3096599999999</v>
+      </c>
+    </row>
+    <row r="6434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6434" t="s">
-        <v>6462</v>
-      </c>
-    </row>
-    <row r="6435" spans="1:1" x14ac:dyDescent="0.3">
+        <v>6463</v>
+      </c>
+      <c r="B6434" s="1">
+        <v>3894.4533999999999</v>
+      </c>
+    </row>
+    <row r="6435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6435" t="s">
-        <v>6463</v>
+        <v>6464</v>
+      </c>
+    </row>
+    <row r="6436" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6436" t="s">
+        <v>6464</v>
+      </c>
+    </row>
+    <row r="6437" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6437" t="s">
+        <v>6465</v>
       </c>
     </row>
   </sheetData>
@@ -71320,19 +71342,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6464</v>
+        <v>6466</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6465</v>
+        <v>6467</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6466</v>
+        <v>6468</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6467</v>
+        <v>6469</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6468</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71343,13 +71365,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71360,13 +71382,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71377,13 +71399,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71394,13 +71416,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71411,13 +71433,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71428,13 +71450,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71445,13 +71467,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71462,13 +71484,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71479,13 +71501,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71496,13 +71518,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71513,13 +71535,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71530,13 +71552,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71547,13 +71569,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71564,13 +71586,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71581,13 +71603,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6469</v>
+        <v>6471</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6470</v>
+        <v>6472</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6471</v>
+        <v>6473</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6434"/>
+  <dimension ref="A1:B6437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64761,6 +64761,36 @@
         <v>3842.18553</v>
       </c>
     </row>
+    <row r="6435">
+      <c r="A6435" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B6435" s="1" t="n">
+        <v>3815.99365</v>
+      </c>
+    </row>
+    <row r="6436">
+      <c r="A6436" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B6436" s="1" t="n">
+        <v>3815.99365</v>
+      </c>
+    </row>
+    <row r="6437">
+      <c r="A6437" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B6437" s="1" t="n">
+        <v>3807.65632</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8438F7BD-D04A-48AC-8D21-ECDDC2E35CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A5BDC5-9B72-4F0D-8233-1852CBE3A7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,25 +11,12 @@
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
     <sheet name="Información" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6523" uniqueCount="6478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6526" uniqueCount="6481">
   <si>
     <t>Fecha</t>
   </si>
@@ -19435,10 +19422,19 @@
     <t>2026/07/06</t>
   </si>
   <si>
+    <t>2026/07/07</t>
+  </si>
+  <si>
+    <t>2026/07/08</t>
+  </si>
+  <si>
+    <t>2026/07/09</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República martes, 7 de julio de 2026 10:59:40 a. m.</t>
+    <t>Descargado de sistema del Banco de la República viernes, 10 de julio de 2026 9:17:56 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19854,7 +19850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6441"/>
+  <dimension ref="A1:B6444"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71368,15 +71364,39 @@
       <c r="A6439" t="s">
         <v>6468</v>
       </c>
+      <c r="B6439" s="1">
+        <v>3830.9999699999998</v>
+      </c>
     </row>
     <row r="6440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6440" t="s">
-        <v>6468</v>
+        <v>6469</v>
+      </c>
+      <c r="B6440" s="1">
+        <v>3804.80485</v>
       </c>
     </row>
     <row r="6441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6441" t="s">
-        <v>6469</v>
+        <v>6470</v>
+      </c>
+      <c r="B6441" s="1">
+        <v>3818.0548600000002</v>
+      </c>
+    </row>
+    <row r="6442" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6442" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="6443" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6443" t="s">
+        <v>6471</v>
+      </c>
+    </row>
+    <row r="6444" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6444" t="s">
+        <v>6472</v>
       </c>
     </row>
   </sheetData>
@@ -71399,19 +71419,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6470</v>
+        <v>6473</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6471</v>
+        <v>6474</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6472</v>
+        <v>6475</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6473</v>
+        <v>6476</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6474</v>
+        <v>6477</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71422,13 +71442,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71439,13 +71459,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71456,13 +71476,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71473,13 +71493,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71490,13 +71510,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71507,13 +71527,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71524,13 +71544,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71541,13 +71561,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71558,13 +71578,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71575,13 +71595,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71592,13 +71612,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71609,13 +71629,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71626,13 +71646,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71643,13 +71663,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71660,13 +71680,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6475</v>
+        <v>6478</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6476</v>
+        <v>6479</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6477</v>
+        <v>6480</v>
       </c>
     </row>
   </sheetData>
